--- a/README.xlsx
+++ b/README.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP ProBook 455 G10\Desktop\project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP ProBook 455 G10\Desktop\project\box-print-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F17991-D2F4-4692-9AC3-518741EA24C4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC446F4-C0EC-4F60-B4FC-F59254B568C4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="141">
   <si>
     <t>iloom / desker / slowbed</t>
   </si>
@@ -454,6 +454,12 @@
   <si>
     <t>인쇄시안 만들기    python renderer.py</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">python guide_maker.py --all  </t>
+  </si>
+  <si>
+    <t>python renderer.py</t>
   </si>
 </sst>
 </file>
@@ -2377,79 +2383,86 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4561DDBD-7E45-475A-BD69-1020A488AB83}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="53" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>138</v>
+      </c>
+      <c r="B17" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/README.xlsx
+++ b/README.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP ProBook 455 G10\Desktop\project\box-print-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC446F4-C0EC-4F60-B4FC-F59254B568C4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A53FE8-2D78-40D0-AE98-DF625159B8ED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="124">
   <si>
     <t>iloom / desker / slowbed</t>
   </si>
@@ -53,9 +53,6 @@
     <t>박스 폭(mm)</t>
   </si>
   <si>
-    <t>박스 높이(mm)</t>
-  </si>
-  <si>
     <t>MADE IN KOREA 
  VIETNAM 
  CHINA</t>
@@ -97,9 +94,6 @@
     <t>width_mm</t>
   </si>
   <si>
-    <t>height_mm</t>
-  </si>
-  <si>
     <t>origin_country</t>
   </si>
   <si>
@@ -178,24 +172,12 @@
     <t>S</t>
   </si>
   <si>
-    <t>210~399</t>
-  </si>
-  <si>
-    <t>200~399</t>
-  </si>
-  <si>
     <t>표준형</t>
   </si>
   <si>
-    <t>400~899</t>
-  </si>
-  <si>
     <t>확대형</t>
   </si>
   <si>
-    <t>900~</t>
-  </si>
-  <si>
     <t>판재형</t>
   </si>
   <si>
@@ -205,39 +187,24 @@
     <t>SS</t>
   </si>
   <si>
-    <t>300~599</t>
-  </si>
-  <si>
-    <t>20~39</t>
-  </si>
-  <si>
     <t>표준형*축소형</t>
   </si>
   <si>
     <t>MS</t>
   </si>
   <si>
-    <t>600~1799</t>
-  </si>
-  <si>
     <t>표준형*표준형</t>
   </si>
   <si>
     <t>MM</t>
   </si>
   <si>
-    <t>40~99</t>
-  </si>
-  <si>
     <t>확대형*축소형</t>
   </si>
   <si>
     <t>LS</t>
   </si>
   <si>
-    <t>1800~</t>
-  </si>
-  <si>
     <t>확대형*표준형</t>
   </si>
   <si>
@@ -250,151 +217,21 @@
     <t>LL</t>
   </si>
   <si>
-    <t>100~</t>
-  </si>
-  <si>
     <t>막대형</t>
   </si>
   <si>
     <t>LONG</t>
   </si>
   <si>
-    <t>200~599</t>
-  </si>
-  <si>
-    <t>LONG_SS</t>
-  </si>
-  <si>
-    <t>LONG_MS</t>
-  </si>
-  <si>
-    <t>LONG_MM</t>
-  </si>
-  <si>
-    <t>1800~2400</t>
-  </si>
-  <si>
-    <t>LONG_LS</t>
-  </si>
-  <si>
-    <t>LONG_LM</t>
-  </si>
-  <si>
-    <t>LONG_LL</t>
-  </si>
-  <si>
     <t>소형</t>
   </si>
   <si>
-    <t>20~209</t>
-  </si>
-  <si>
-    <t>70~199</t>
-  </si>
-  <si>
-    <t>COMPACT_M</t>
-  </si>
-  <si>
-    <t>300~499</t>
-  </si>
-  <si>
-    <t>150~299</t>
-  </si>
-  <si>
-    <t>BASIC_S</t>
-  </si>
-  <si>
-    <t>500~899</t>
-  </si>
-  <si>
-    <t>BASIC_M</t>
-  </si>
-  <si>
-    <t>900~1250</t>
-  </si>
-  <si>
-    <t>500~950</t>
-  </si>
-  <si>
-    <t>BASIC_L</t>
-  </si>
-  <si>
-    <t>350~649</t>
-  </si>
-  <si>
-    <t>250~449</t>
-  </si>
-  <si>
-    <t>PANEL_S</t>
-  </si>
-  <si>
-    <t>650~1199</t>
-  </si>
-  <si>
-    <t>450~749</t>
-  </si>
-  <si>
-    <t>PANEL_M</t>
-  </si>
-  <si>
-    <t>1200~1450</t>
-  </si>
-  <si>
-    <t>100~150</t>
-  </si>
-  <si>
-    <t>750~850</t>
-  </si>
-  <si>
-    <t>PANEL_L</t>
-  </si>
-  <si>
-    <t>400~649</t>
-  </si>
-  <si>
-    <t>40~79</t>
-  </si>
-  <si>
-    <t>LONG_S</t>
-  </si>
-  <si>
-    <t>650~999</t>
-  </si>
-  <si>
-    <t>80~119</t>
-  </si>
-  <si>
-    <t>LONG_M</t>
-  </si>
-  <si>
-    <t>1000~1400</t>
-  </si>
-  <si>
-    <t>80~150</t>
-  </si>
-  <si>
-    <t>120~250</t>
-  </si>
-  <si>
-    <t>LONG_L</t>
-  </si>
-  <si>
-    <t>_</t>
-  </si>
-  <si>
     <t>상하분리형</t>
   </si>
   <si>
     <t>LID</t>
   </si>
   <si>
-    <t>LID_M</t>
-  </si>
-  <si>
-    <t>file_name</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>brand</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -460,6 +297,154 @@
   </si>
   <si>
     <t>python renderer.py</t>
+  </si>
+  <si>
+    <t>L</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>W</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>H</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>210 ~ 399</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>400 ~ 899</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>900 ~</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>300 ~ 599</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>600 ~ 1799</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1800 ~ </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>200 ~ 599</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1800 ~ 2400</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>20 ~ 209</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>300 ~ 499</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>500 ~ 899</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>900 ~ 1250</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>350 ~ 649</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>650 ~ 1199</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1200 ~ 1450</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>400 ~ 649</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>650 ~ 999</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000 ~ 1400</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>200 ~ 399</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">900 ~ </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>20 ~ 39</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>40 ~ 99</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">100 ~ </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>70 ~ 199</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>150 ~ 299</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>500 ~ 950</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>100 ~ 150</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>40 ~ 79</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>80 ~ 150</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>250 ~ 449</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>450 ~ 749</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>750 ~ 850</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>80 ~ 119</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>120 ~ 250</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1034,7 +1019,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1043,6 +1028,9 @@
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1403,10 +1391,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="8" width="16.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="108" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="84" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1431,10 +1425,10 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -1446,69 +1440,63 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>19</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>21</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>25</v>
       </c>
-      <c r="M2" t="s">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>26</v>
       </c>
-      <c r="N2" t="s">
+      <c r="B3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
         <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>31</v>
       </c>
       <c r="G3">
         <v>700</v>
@@ -1516,40 +1504,37 @@
       <c r="H3">
         <v>600</v>
       </c>
-      <c r="I3">
-        <v>900</v>
+      <c r="I3" t="s">
+        <v>30</v>
       </c>
       <c r="J3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="2">
+        <v>4.2361111111111106E-2</v>
+      </c>
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s">
         <v>32</v>
       </c>
-      <c r="K3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L3" s="2">
-        <v>4.2361111111111106E-2</v>
-      </c>
-      <c r="M3" t="s">
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>33</v>
       </c>
-      <c r="N3" t="s">
+      <c r="B4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="C4" t="s">
         <v>35</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E4" t="s">
         <v>36</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" t="s">
-        <v>39</v>
       </c>
       <c r="G4">
         <v>125</v>
@@ -1557,40 +1542,37 @@
       <c r="H4">
         <v>125</v>
       </c>
-      <c r="I4">
-        <v>80</v>
+      <c r="I4" t="s">
+        <v>38</v>
       </c>
       <c r="J4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="2">
+        <v>4.2361111111111106E-2</v>
+      </c>
+      <c r="L4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
         <v>40</v>
       </c>
-      <c r="K4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L4" s="2">
-        <v>4.2361111111111106E-2</v>
-      </c>
-      <c r="M4" t="s">
-        <v>33</v>
-      </c>
-      <c r="N4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="E5" t="s">
         <v>41</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
         <v>42</v>
-      </c>
-      <c r="E5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" t="s">
-        <v>44</v>
       </c>
       <c r="G5">
         <v>1590</v>
@@ -1598,781 +1580,713 @@
       <c r="H5">
         <v>980</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="2">
+        <v>4.2361111111111106E-2</v>
+      </c>
+      <c r="L5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="F12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:13" s="3" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="J5" t="s">
+      <c r="F19" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="4"/>
+      <c r="B29" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="K5" t="s">
-        <v>10</v>
-      </c>
-      <c r="L5" s="2">
-        <v>4.2361111111111106E-2</v>
-      </c>
-      <c r="M5" t="s">
-        <v>33</v>
-      </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="F12" s="3" t="s">
+      <c r="E30" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+    </row>
+    <row r="38" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B14" t="s">
+    </row>
+    <row r="39" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="F39" s="3">
+        <v>300</v>
+      </c>
+      <c r="G39" s="3">
+        <v>300</v>
+      </c>
+      <c r="H39" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="E40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40" s="3">
+        <v>600</v>
+      </c>
+      <c r="G40" s="3">
+        <v>600</v>
+      </c>
+      <c r="H40" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="4"/>
+      <c r="B41" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G14" t="s">
+      <c r="C41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G41" s="3">
         <v>50</v>
       </c>
-      <c r="I14" t="str">
-        <f>C14&amp;"_"&amp;E14</f>
-        <v>BASIC_S</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15" t="s">
-        <v>52</v>
-      </c>
-      <c r="I15" t="str">
-        <f t="shared" ref="I15:I23" si="0">C15&amp;"_"&amp;E15</f>
-        <v>BASIC_M</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16" t="s">
-        <v>54</v>
-      </c>
-      <c r="I16" t="str">
-        <f t="shared" si="0"/>
-        <v>BASIC_L</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18" t="s">
-        <v>59</v>
-      </c>
-      <c r="H18" t="s">
-        <v>58</v>
-      </c>
-      <c r="I18" t="str">
-        <f t="shared" si="0"/>
-        <v>PANEL_SS</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C19" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="H41" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="4"/>
+      <c r="B42" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="G19" t="s">
-        <v>59</v>
-      </c>
-      <c r="H19" t="s">
-        <v>62</v>
-      </c>
-      <c r="I19" t="str">
-        <f t="shared" si="0"/>
-        <v>PANEL_MS</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="C42" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E20" t="s">
-        <v>64</v>
-      </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="D42" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F42" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G42" s="3">
+        <v>50</v>
+      </c>
+      <c r="H42" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="4"/>
+      <c r="B43" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H20" t="s">
-        <v>62</v>
-      </c>
-      <c r="I20" t="str">
-        <f t="shared" si="0"/>
-        <v>PANEL_MM</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C21" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="C43" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E21" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" t="s">
-        <v>68</v>
-      </c>
-      <c r="G21" t="s">
-        <v>59</v>
-      </c>
-      <c r="H21" t="s">
-        <v>68</v>
-      </c>
-      <c r="I21" t="str">
-        <f t="shared" si="0"/>
-        <v>PANEL_LS</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C22" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" t="s">
-        <v>69</v>
-      </c>
-      <c r="E22" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" t="s">
-        <v>68</v>
-      </c>
-      <c r="G22" t="s">
-        <v>65</v>
-      </c>
-      <c r="H22" t="s">
-        <v>68</v>
-      </c>
-      <c r="I22" t="str">
-        <f t="shared" si="0"/>
-        <v>PANEL_LM</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C23" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" t="s">
-        <v>72</v>
-      </c>
-      <c r="F23" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" t="s">
-        <v>73</v>
-      </c>
-      <c r="H23" t="s">
-        <v>68</v>
-      </c>
-      <c r="I23" t="str">
-        <f t="shared" si="0"/>
-        <v>PANEL_LL</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" t="s">
-        <v>56</v>
-      </c>
-      <c r="E25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F25" t="s">
-        <v>76</v>
-      </c>
-      <c r="G25" t="s">
-        <v>59</v>
-      </c>
-      <c r="I25" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C26" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" t="s">
-        <v>60</v>
-      </c>
-      <c r="E26" t="s">
-        <v>61</v>
-      </c>
-      <c r="F26" t="s">
-        <v>62</v>
-      </c>
-      <c r="G26" t="s">
-        <v>59</v>
-      </c>
-      <c r="I26" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" t="s">
-        <v>63</v>
-      </c>
-      <c r="E27" t="s">
-        <v>64</v>
-      </c>
-      <c r="F27" t="s">
-        <v>62</v>
-      </c>
-      <c r="G27" t="s">
-        <v>65</v>
-      </c>
-      <c r="I27" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C28" t="s">
-        <v>75</v>
-      </c>
-      <c r="D28" t="s">
-        <v>66</v>
-      </c>
-      <c r="E28" t="s">
-        <v>67</v>
-      </c>
-      <c r="F28" t="s">
-        <v>80</v>
-      </c>
-      <c r="G28" t="s">
-        <v>59</v>
-      </c>
-      <c r="I28" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C29" t="s">
-        <v>75</v>
-      </c>
-      <c r="D29" t="s">
-        <v>69</v>
-      </c>
-      <c r="E29" t="s">
-        <v>70</v>
-      </c>
-      <c r="F29" t="s">
-        <v>80</v>
-      </c>
-      <c r="G29" t="s">
-        <v>65</v>
-      </c>
-      <c r="I29" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C30" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30" t="s">
-        <v>71</v>
-      </c>
-      <c r="E30" t="s">
-        <v>72</v>
-      </c>
-      <c r="F30" t="s">
-        <v>80</v>
-      </c>
-      <c r="G30" t="s">
-        <v>73</v>
-      </c>
-      <c r="I30" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" t="s">
-        <v>38</v>
-      </c>
-      <c r="E32" t="s">
-        <v>31</v>
-      </c>
-      <c r="F32" t="s">
-        <v>85</v>
-      </c>
-      <c r="G32" t="s">
-        <v>86</v>
-      </c>
-      <c r="I32" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="D43" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E36" t="s">
-        <v>48</v>
-      </c>
-      <c r="F36" t="s">
-        <v>88</v>
-      </c>
-      <c r="G36" t="s">
-        <v>89</v>
-      </c>
-      <c r="I36" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" t="s">
-        <v>51</v>
-      </c>
-      <c r="E37" t="s">
-        <v>31</v>
-      </c>
-      <c r="F37" t="s">
-        <v>91</v>
-      </c>
-      <c r="G37" t="s">
-        <v>88</v>
-      </c>
-      <c r="I37" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C38" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" t="s">
-        <v>53</v>
-      </c>
-      <c r="E38" t="s">
-        <v>44</v>
-      </c>
-      <c r="F38" t="s">
-        <v>93</v>
-      </c>
-      <c r="G38" t="s">
-        <v>94</v>
-      </c>
-      <c r="I38" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
-        <v>55</v>
-      </c>
-      <c r="C40" t="s">
-        <v>43</v>
-      </c>
-      <c r="D40" t="s">
-        <v>47</v>
-      </c>
-      <c r="E40" t="s">
-        <v>48</v>
-      </c>
-      <c r="F40" t="s">
-        <v>96</v>
-      </c>
-      <c r="G40" t="s">
-        <v>59</v>
-      </c>
-      <c r="H40" t="s">
-        <v>97</v>
-      </c>
-      <c r="I40" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C41" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" t="s">
-        <v>51</v>
-      </c>
-      <c r="E41" t="s">
-        <v>31</v>
-      </c>
-      <c r="F41" t="s">
-        <v>99</v>
-      </c>
-      <c r="G41" t="s">
-        <v>65</v>
-      </c>
-      <c r="H41" t="s">
-        <v>100</v>
-      </c>
-      <c r="I41" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C42" t="s">
-        <v>43</v>
-      </c>
-      <c r="D42" t="s">
-        <v>53</v>
-      </c>
-      <c r="E42" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" t="s">
-        <v>102</v>
-      </c>
-      <c r="G42" t="s">
-        <v>103</v>
-      </c>
-      <c r="H42" t="s">
-        <v>104</v>
-      </c>
-      <c r="I42" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B44" t="s">
-        <v>74</v>
-      </c>
-      <c r="C44" t="s">
-        <v>75</v>
-      </c>
-      <c r="D44" t="s">
-        <v>47</v>
-      </c>
-      <c r="E44" t="s">
-        <v>48</v>
-      </c>
-      <c r="F44" t="s">
-        <v>106</v>
-      </c>
-      <c r="G44" t="s">
-        <v>59</v>
-      </c>
-      <c r="H44" t="s">
-        <v>107</v>
-      </c>
-      <c r="I44" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C45" t="s">
-        <v>75</v>
-      </c>
-      <c r="D45" t="s">
-        <v>51</v>
-      </c>
-      <c r="E45" t="s">
-        <v>31</v>
-      </c>
-      <c r="F45" t="s">
-        <v>109</v>
-      </c>
-      <c r="G45" t="s">
-        <v>107</v>
-      </c>
-      <c r="H45" t="s">
-        <v>110</v>
-      </c>
-      <c r="I45" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C46" t="s">
-        <v>75</v>
-      </c>
-      <c r="D46" t="s">
-        <v>53</v>
-      </c>
-      <c r="E46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F46" t="s">
-        <v>112</v>
-      </c>
-      <c r="G46" t="s">
-        <v>113</v>
-      </c>
-      <c r="H46" t="s">
-        <v>114</v>
-      </c>
-      <c r="I46" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>124</v>
-      </c>
-      <c r="B50" t="s">
-        <v>46</v>
-      </c>
-      <c r="C50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D50" t="s">
-        <v>47</v>
-      </c>
-      <c r="E50" t="s">
-        <v>48</v>
-      </c>
-      <c r="F50">
-        <v>300</v>
-      </c>
-      <c r="G50">
-        <v>300</v>
-      </c>
-      <c r="H50">
-        <v>200</v>
-      </c>
-      <c r="I50" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C51" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" t="s">
-        <v>51</v>
-      </c>
-      <c r="E51" t="s">
-        <v>31</v>
-      </c>
-      <c r="F51">
-        <v>600</v>
-      </c>
-      <c r="G51">
-        <v>600</v>
-      </c>
-      <c r="H51">
-        <v>400</v>
-      </c>
-      <c r="I51" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I52" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B53" t="s">
-        <v>55</v>
-      </c>
-      <c r="C53" t="s">
-        <v>43</v>
-      </c>
-      <c r="D53" t="s">
-        <v>51</v>
-      </c>
-      <c r="E53" t="s">
-        <v>31</v>
-      </c>
-      <c r="F53">
-        <v>1000</v>
-      </c>
-      <c r="G53">
-        <v>50</v>
-      </c>
-      <c r="H53">
-        <v>500</v>
-      </c>
-      <c r="I53" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I54" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B55" t="s">
-        <v>74</v>
-      </c>
-      <c r="C55" t="s">
-        <v>75</v>
-      </c>
-      <c r="D55" t="s">
-        <v>51</v>
-      </c>
-      <c r="E55" t="s">
-        <v>31</v>
-      </c>
-      <c r="F55">
-        <v>1200</v>
-      </c>
-      <c r="G55">
-        <v>50</v>
-      </c>
-      <c r="H55">
-        <v>90</v>
-      </c>
-      <c r="I55" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I56" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B57" t="s">
-        <v>117</v>
-      </c>
-      <c r="C57" t="s">
-        <v>118</v>
-      </c>
-      <c r="D57" t="s">
-        <v>51</v>
-      </c>
-      <c r="E57" t="s">
-        <v>31</v>
-      </c>
-      <c r="F57">
+      <c r="E43" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F43" s="3">
         <v>2065</v>
       </c>
-      <c r="G57">
+      <c r="G43" s="3">
         <v>340</v>
       </c>
-      <c r="H57">
+      <c r="H43" s="3">
         <v>1165</v>
       </c>
-      <c r="I57" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H58" t="s">
-        <v>116</v>
-      </c>
-    </row>
+    </row>
+    <row r="44" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="13">
+    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B17:B22"/>
+    <mergeCell ref="B23:B28"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B39:B40"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="F12:H12"/>
+    <mergeCell ref="A14:A29"/>
+    <mergeCell ref="A30:A38"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2391,73 +2305,73 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>126</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>128</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>129</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>132</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>136</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
